--- a/data/TMP.MI.xlsx
+++ b/data/TMP.MI.xlsx
@@ -21394,6 +21394,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="915">
+      <c r="A915" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B915" t="n">
+        <v>0</v>
+      </c>
+      <c r="C915" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="D915" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="E915" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="F915" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="G915" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TMP.MI.xlsx
+++ b/data/TMP.MI.xlsx
@@ -21417,6 +21417,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="916">
+      <c r="A916" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B916" t="n">
+        <v>0</v>
+      </c>
+      <c r="C916" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="D916" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="E916" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="F916" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="G916" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B917" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C917" t="n">
+        <v>5.94000005722046</v>
+      </c>
+      <c r="D917" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="E917" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="F917" t="n">
+        <v>5.94000005722046</v>
+      </c>
+      <c r="G917" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TMP.MI.xlsx
+++ b/data/TMP.MI.xlsx
@@ -21463,6 +21463,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="918">
+      <c r="A918" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B918" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C918" t="n">
+        <v>5.82000017166138</v>
+      </c>
+      <c r="D918" t="n">
+        <v>5.51999998092651</v>
+      </c>
+      <c r="E918" t="n">
+        <v>5.65999984741211</v>
+      </c>
+      <c r="F918" t="n">
+        <v>5.6399998664856</v>
+      </c>
+      <c r="G918" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TMP.MI.xlsx
+++ b/data/TMP.MI.xlsx
@@ -21304,22 +21304,22 @@
     </row>
     <row r="911">
       <c r="A911" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B911" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="C911" t="n">
-        <v>6.19999980926514</v>
+        <v>6.03999996185303</v>
       </c>
       <c r="D911" t="n">
-        <v>5.80000019073486</v>
+        <v>6.03999996185303</v>
       </c>
       <c r="E911" t="n">
-        <v>5.82000017166138</v>
+        <v>6.03999996185303</v>
       </c>
       <c r="F911" t="n">
-        <v>6.19999980926514</v>
+        <v>6.03999996185303</v>
       </c>
       <c r="G911" t="s">
         <v>7</v>
@@ -21327,19 +21327,19 @@
     </row>
     <row r="912">
       <c r="A912" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B912" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="C912" t="n">
         <v>6.19999980926514</v>
       </c>
       <c r="D912" t="n">
-        <v>6.19999980926514</v>
+        <v>5.80000019073486</v>
       </c>
       <c r="E912" t="n">
-        <v>6.19999980926514</v>
+        <v>5.82000017166138</v>
       </c>
       <c r="F912" t="n">
         <v>6.19999980926514</v>
@@ -21350,22 +21350,22 @@
     </row>
     <row r="913">
       <c r="A913" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B913" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="C913" t="n">
-        <v>5.90000009536743</v>
+        <v>6.19999980926514</v>
       </c>
       <c r="D913" t="n">
-        <v>5.71999979019165</v>
+        <v>6.19999980926514</v>
       </c>
       <c r="E913" t="n">
-        <v>5.90000009536743</v>
+        <v>6.19999980926514</v>
       </c>
       <c r="F913" t="n">
-        <v>5.90000009536743</v>
+        <v>6.19999980926514</v>
       </c>
       <c r="G913" t="s">
         <v>7</v>
@@ -21373,22 +21373,22 @@
     </row>
     <row r="914">
       <c r="A914" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B914" t="n">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="C914" t="n">
-        <v>6.09999990463257</v>
+        <v>5.90000009536743</v>
       </c>
       <c r="D914" t="n">
-        <v>5.94000005722046</v>
+        <v>5.71999979019165</v>
       </c>
       <c r="E914" t="n">
-        <v>5.94000005722046</v>
+        <v>5.90000009536743</v>
       </c>
       <c r="F914" t="n">
-        <v>6.09999990463257</v>
+        <v>5.90000009536743</v>
       </c>
       <c r="G914" t="s">
         <v>7</v>
@@ -21396,19 +21396,19 @@
     </row>
     <row r="915">
       <c r="A915" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B915" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="C915" t="n">
         <v>6.09999990463257</v>
       </c>
       <c r="D915" t="n">
-        <v>6.09999990463257</v>
+        <v>5.94000005722046</v>
       </c>
       <c r="E915" t="n">
-        <v>6.09999990463257</v>
+        <v>5.94000005722046</v>
       </c>
       <c r="F915" t="n">
         <v>6.09999990463257</v>
@@ -21419,7 +21419,7 @@
     </row>
     <row r="916">
       <c r="A916" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B916" t="n">
         <v>0</v>
@@ -21442,22 +21442,22 @@
     </row>
     <row r="917">
       <c r="A917" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B917" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C917" t="n">
-        <v>5.94000005722046</v>
+        <v>6.09999990463257</v>
       </c>
       <c r="D917" t="n">
-        <v>5.69999980926514</v>
+        <v>6.09999990463257</v>
       </c>
       <c r="E917" t="n">
-        <v>5.80000019073486</v>
+        <v>6.09999990463257</v>
       </c>
       <c r="F917" t="n">
-        <v>5.94000005722046</v>
+        <v>6.09999990463257</v>
       </c>
       <c r="G917" t="s">
         <v>7</v>
@@ -21465,24 +21465,47 @@
     </row>
     <row r="918">
       <c r="A918" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B918" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="C918" t="n">
-        <v>5.82000017166138</v>
+        <v>5.94000005722046</v>
       </c>
       <c r="D918" t="n">
-        <v>5.51999998092651</v>
+        <v>5.69999980926514</v>
       </c>
       <c r="E918" t="n">
-        <v>5.65999984741211</v>
+        <v>5.80000019073486</v>
       </c>
       <c r="F918" t="n">
-        <v>5.6399998664856</v>
+        <v>5.94000005722046</v>
       </c>
       <c r="G918" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B919" t="n">
+        <v>800</v>
+      </c>
+      <c r="C919" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="D919" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E919" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F919" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="G919" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TMP.MI.xlsx
+++ b/data/TMP.MI.xlsx
@@ -24321,6 +24321,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="922">
+      <c r="A922" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B922" t="n">
+        <v>6200</v>
+      </c>
+      <c r="C922" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="D922" t="n">
+        <v>5</v>
+      </c>
+      <c r="E922" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="F922" t="n">
+        <v>5.21999979019165</v>
+      </c>
+      <c r="G922" t="n">
+        <v>5.21999979019165</v>
+      </c>
+      <c r="H922" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TMP.MI.xlsx
+++ b/data/TMP.MI.xlsx
@@ -24347,6 +24347,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="923">
+      <c r="A923" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B923" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C923" t="n">
+        <v>5.26000022888184</v>
+      </c>
+      <c r="D923" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="E923" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="F923" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="G923" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="H923" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TMP.MI.xlsx
+++ b/data/TMP.MI.xlsx
@@ -21693,6 +21693,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="928">
+      <c r="A928" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B928" t="n">
+        <v>0</v>
+      </c>
+      <c r="C928" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="D928" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="E928" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="F928" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="G928" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B929" t="n">
+        <v>800</v>
+      </c>
+      <c r="C929" t="n">
+        <v>5.17999982833862</v>
+      </c>
+      <c r="D929" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="E929" t="n">
+        <v>5.17999982833862</v>
+      </c>
+      <c r="F929"/>
+      <c r="G929" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TMP.MI.xlsx
+++ b/data/TMP.MI.xlsx
@@ -21773,13 +21773,36 @@
         <v>5.5</v>
       </c>
       <c r="D931" t="n">
-        <v>4.80000019073486</v>
+        <v>4.65999984741211</v>
       </c>
       <c r="E931" t="n">
         <v>5.23999977111816</v>
       </c>
-      <c r="F931"/>
+      <c r="F931" t="n">
+        <v>4.65999984741211</v>
+      </c>
       <c r="G931" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B932" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C932" t="n">
+        <v>4.71000003814697</v>
+      </c>
+      <c r="D932" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E932" t="n">
+        <v>4.6100001335144</v>
+      </c>
+      <c r="F932"/>
+      <c r="G932" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TMP.MI.xlsx
+++ b/data/TMP.MI.xlsx
@@ -21801,8 +21801,31 @@
       <c r="E932" t="n">
         <v>4.6100001335144</v>
       </c>
-      <c r="F932"/>
+      <c r="F932" t="n">
+        <v>4.5</v>
+      </c>
       <c r="G932" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B933" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C933" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D933" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E933" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F933"/>
+      <c r="G933" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TMP.MI.xlsx
+++ b/data/TMP.MI.xlsx
@@ -21824,7 +21824,9 @@
       <c r="E933" t="n">
         <v>4.59999990463257</v>
       </c>
-      <c r="F933"/>
+      <c r="F933" t="n">
+        <v>4.59999990463257</v>
+      </c>
       <c r="G933" t="s">
         <v>7</v>
       </c>

--- a/data/TMP.MI.xlsx
+++ b/data/TMP.MI.xlsx
@@ -21831,6 +21831,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="934">
+      <c r="A934" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B934" t="n">
+        <v>0</v>
+      </c>
+      <c r="C934" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D934" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E934" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F934" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G934" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TMP.MI.xlsx
+++ b/data/TMP.MI.xlsx
@@ -21877,6 +21877,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="936">
+      <c r="A936" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B936" t="n">
+        <v>1400</v>
+      </c>
+      <c r="C936" t="n">
+        <v>4.48999977111816</v>
+      </c>
+      <c r="D936" t="n">
+        <v>4.19000005722046</v>
+      </c>
+      <c r="E936" t="n">
+        <v>4.48999977111816</v>
+      </c>
+      <c r="F936" t="n">
+        <v>4.19000005722046</v>
+      </c>
+      <c r="G936" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TMP.MI.xlsx
+++ b/data/TMP.MI.xlsx
@@ -27638,6 +27638,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="941">
+      <c r="A941" t="s">
+        <v>9</v>
+      </c>
+      <c r="B941" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C941" t="n">
+        <v>3.91000008583069</v>
+      </c>
+      <c r="D941" t="n">
+        <v>3.91000008583069</v>
+      </c>
+      <c r="E941" t="n">
+        <v>3.91000008583069</v>
+      </c>
+      <c r="F941" t="n">
+        <v>3.91000008583069</v>
+      </c>
+      <c r="G941" t="n">
+        <v>3.91000008583069</v>
+      </c>
+      <c r="H941" t="n">
+        <v>0</v>
+      </c>
+      <c r="I941" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TMP.MI.xlsx
+++ b/data/TMP.MI.xlsx
@@ -27667,6 +27667,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="942">
+      <c r="A942" t="s">
+        <v>9</v>
+      </c>
+      <c r="B942" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C942" t="n">
+        <v>3.91000008583069</v>
+      </c>
+      <c r="D942" t="n">
+        <v>3.91000008583069</v>
+      </c>
+      <c r="E942" t="n">
+        <v>3.91000008583069</v>
+      </c>
+      <c r="F942" t="n">
+        <v>3.91000008583069</v>
+      </c>
+      <c r="G942" t="n">
+        <v>3.91000008583069</v>
+      </c>
+      <c r="H942" t="n">
+        <v>0</v>
+      </c>
+      <c r="I942" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="s">
+        <v>9</v>
+      </c>
+      <c r="B943" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C943" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="D943" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="E943" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="F943" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="G943" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="H943" t="n">
+        <v>400</v>
+      </c>
+      <c r="I943" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TMP.MI.xlsx
+++ b/data/TMP.MI.xlsx
@@ -27725,6 +27725,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="944">
+      <c r="A944" t="s">
+        <v>9</v>
+      </c>
+      <c r="B944" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C944" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="D944" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="E944" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="F944" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="G944" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="H944" t="n">
+        <v>0</v>
+      </c>
+      <c r="I944" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="s">
+        <v>9</v>
+      </c>
+      <c r="B945" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C945" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="D945" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="E945" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="F945" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="G945" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="H945" t="n">
+        <v>200</v>
+      </c>
+      <c r="I945" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TMP.MI.xlsx
+++ b/data/TMP.MI.xlsx
@@ -27783,6 +27783,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="946">
+      <c r="A946" t="s">
+        <v>9</v>
+      </c>
+      <c r="B946" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C946" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="D946" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="E946" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="F946" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="G946" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="H946" t="n">
+        <v>0</v>
+      </c>
+      <c r="I946" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="s">
+        <v>9</v>
+      </c>
+      <c r="B947" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C947" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="D947" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="E947" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="F947" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="G947" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="H947" t="n">
+        <v>200</v>
+      </c>
+      <c r="I947" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TMP.MI.xlsx
+++ b/data/TMP.MI.xlsx
@@ -27841,6 +27841,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="948">
+      <c r="A948" t="s">
+        <v>9</v>
+      </c>
+      <c r="B948" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C948" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="D948" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="E948" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="F948" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="G948" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="H948" t="n">
+        <v>0</v>
+      </c>
+      <c r="I948" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TMP.MI.xlsx
+++ b/data/TMP.MI.xlsx
@@ -27870,6 +27870,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="949">
+      <c r="A949" t="s">
+        <v>9</v>
+      </c>
+      <c r="B949" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C949" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="D949" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="E949" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="F949" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="G949" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="H949" t="n">
+        <v>0</v>
+      </c>
+      <c r="I949" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="s">
+        <v>9</v>
+      </c>
+      <c r="B950" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C950" t="n">
+        <v>3.94000005722046</v>
+      </c>
+      <c r="D950" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="E950" t="n">
+        <v>3.94000005722046</v>
+      </c>
+      <c r="F950" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="G950" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="H950" t="n">
+        <v>3600</v>
+      </c>
+      <c r="I950" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
